--- a/작업요청서.xlsx
+++ b/작업요청서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d59a48d3e0a0116/바탕 화면/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seo sang won\001.작업파일\004. 출판친구\018. 안티그래비티\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{903CC7C1-1BC5-43C0-9678-151E117D9DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C9A142-4438-4D72-8AF0-E1890AB4138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="13824" windowHeight="8400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(주)한국리더십센터" sheetId="9" r:id="rId1"/>
@@ -6158,18 +6158,6 @@
     <xf numFmtId="3" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6236,11 +6224,23 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -39191,22 +39191,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="52.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
     </row>
     <row r="2" spans="2:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="19"/>
@@ -39248,25 +39248,25 @@
       <c r="B4" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="69"/>
+      <c r="D4" s="65"/>
       <c r="E4" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="69"/>
-      <c r="H4" s="70" t="s">
+      <c r="G4" s="65"/>
+      <c r="H4" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="70"/>
-      <c r="J4" s="71">
+      <c r="I4" s="66"/>
+      <c r="J4" s="67">
         <v>46260</v>
       </c>
-      <c r="K4" s="71"/>
+      <c r="K4" s="67"/>
       <c r="L4" s="29" t="s">
         <v>4</v>
       </c>
@@ -39284,25 +39284,25 @@
       <c r="B5" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="75" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="76" t="s">
+      <c r="K5" s="71"/>
+      <c r="L5" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="78"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="74"/>
     </row>
     <row r="6" spans="2:16" s="48" customFormat="1" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="32" t="s">
@@ -39323,66 +39323,66 @@
       <c r="O6" s="47"/>
     </row>
     <row r="7" spans="2:16" s="48" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="81" t="s">
+      <c r="C7" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="J7" s="60" t="s">
+      <c r="J7" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="60" t="s">
+      <c r="K7" s="84" t="s">
         <v>0</v>
       </c>
       <c r="L7" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="62" t="s">
+      <c r="N7" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="84" t="s">
+      <c r="O7" s="81" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:16" s="48" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="80"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
       <c r="L8" s="34">
         <v>204</v>
       </c>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="85"/>
+      <c r="M8" s="59"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="82"/>
     </row>
     <row r="9" spans="2:16" s="48" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="45" t="s">
@@ -39537,26 +39537,32 @@
       </c>
       <c r="P12" s="41"/>
     </row>
-    <row r="13" spans="2:16" ht="173.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="64" t="s">
+    <row r="13" spans="2:16" ht="300" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="66"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="61"/>
+      <c r="M13" s="61"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="B13:O13"/>
     <mergeCell ref="B1:O1"/>
@@ -39573,12 +39579,6 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="O7:O8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H12">
